--- a/public/data/productividad-atraccion.xlsx
+++ b/public/data/productividad-atraccion.xlsx
@@ -69,8 +69,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,63 +757,63 @@
         <v>NOMBRE</v>
       </c>
       <c r="B1" t="str">
-        <v>TIEMPO CON TACTICAL</v>
+        <v>FECHA INGRESO</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>VALESKA</v>
       </c>
-      <c r="B2" t="str">
-        <v>4 MESES</v>
+      <c r="B2" s="1">
+        <v>46091</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>YESSENIA</v>
       </c>
-      <c r="B3" t="str">
-        <v>7 MESES</v>
+      <c r="B3" s="1">
+        <v>46001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>KARINA</v>
       </c>
-      <c r="B4" t="str">
-        <v>1 AÑO 10 MESES</v>
+      <c r="B4" s="1">
+        <v>45545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>ANDREA</v>
       </c>
-      <c r="B5" t="str">
-        <v>9 MESES</v>
+      <c r="B5" s="1">
+        <v>45940</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>MAYRA</v>
       </c>
-      <c r="B6" t="str">
-        <v>1 MES</v>
+      <c r="B6" s="1">
+        <v>46183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>GERARDO</v>
       </c>
-      <c r="B7" t="str">
-        <v>1 MES</v>
+      <c r="B7" s="1">
+        <v>46183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>ELIUD</v>
       </c>
-      <c r="B8" t="str">
-        <v>3 MESES</v>
+      <c r="B8" s="1">
+        <v>46122</v>
       </c>
     </row>
   </sheetData>
